--- a/FreeLayout/obj/Release/Package/PackageTmp/Textfile/mau upload WI.xlsx
+++ b/FreeLayout/obj/Release/Package/PackageTmp/Textfile/mau upload WI.xlsx
@@ -1,71 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\He thong\Minh 2020\Thang 8.2021\Free loacation mcs web\FreeLayout\Textfile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SCM Inovation2\SCM_Inovation\FreeLayout\Textfile\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{877D96E3-A987-424B-B667-3C32C6E70D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-28920" yWindow="-810" windowWidth="29040" windowHeight="15720" xr2:uid="{F8DABD14-1A58-4313-A364-E3A20E4E1045}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Material</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>InsertDate</t>
-  </si>
-  <si>
-    <t>Userid</t>
-  </si>
-  <si>
-    <t>NULL</t>
-  </si>
-  <si>
-    <t>PFKM1255ZA1-AW65</t>
-  </si>
-  <si>
-    <t>AWW2429C4DC0-0C5</t>
-  </si>
-  <si>
-    <t>/Uploads/mau insert inventory PC.xlsx</t>
-  </si>
-  <si>
-    <t>/Uploads/letter_sakurai.pdf</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -95,9 +67,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -132,7 +103,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -144,7 +115,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -161,9 +132,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -191,14 +162,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -226,6 +214,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -377,86 +382,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57415A2-A7EF-4245-ABD1-904EBAE91266}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="3" max="3" width="43.28515625" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1">
-        <v>44425.345277777778</v>
-      </c>
-      <c r="G2">
-        <v>2012757</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="1">
-        <v>44425.345277777778</v>
-      </c>
-      <c r="G3">
-        <v>2012757</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>